--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DB8EBB-19A3-43D6-9CC6-2C1D45B33839}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C18E7F8-194A-46F3-B2EC-243F5AD07222}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3669" yWindow="3669" windowWidth="24685" windowHeight="13148" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Errors by Device" sheetId="1" r:id="rId1"/>
+    <sheet name="Activity" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" fullPrecision="0"/>
 </workbook>

--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C18E7F8-194A-46F3-B2EC-243F5AD07222}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAFA437-3894-41BA-AFF4-BFE60A5439DD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3669" yWindow="3669" windowWidth="24685" windowHeight="13148" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullPrecision="0"/>
+  <calcPr calcId="181029" fullPrecision="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -59,6 +59,18 @@
   </si>
   <si>
     <t>Device Activity</t>
+  </si>
+  <si>
+    <t>Maintenance status</t>
+  </si>
+  <si>
+    <t>&lt;deviceApprovalStatus&gt;</t>
+  </si>
+  <si>
+    <t>&lt;deviceMaintenanceStatus&gt;</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -586,56 +598,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="26.35546875" customWidth="1"/>
     <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" ht="20.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
@@ -645,11 +659,17 @@
       <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
@@ -659,7 +679,13 @@
       <c r="C8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>11</v>
       </c>
     </row>

--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_activity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\stefan\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAFA437-3894-41BA-AFF4-BFE60A5439DD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB64437-6E89-40AA-9ACC-9CB9092CFB3E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35571" yWindow="1329" windowWidth="22989" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Last Upload</t>
   </si>
   <si>
-    <t>Total Tests Run During Period</t>
-  </si>
-  <si>
     <t>LGA: &lt;Lgas&gt;</t>
   </si>
   <si>
@@ -53,9 +50,6 @@
   </si>
   <si>
     <t>&lt;lastUploadOn&gt;</t>
-  </si>
-  <si>
-    <t>&lt;totalResults&gt;</t>
   </si>
   <si>
     <t>Device Activity</t>
@@ -201,22 +195,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -598,95 +583,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="26.35546875" customWidth="1"/>
     <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="29.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\stefan\aspect\api\templates\device_activity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB64437-6E89-40AA-9ACC-9CB9092CFB3E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A21402-CFE7-4CC8-9D53-349849BEEB26}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35571" yWindow="1329" windowWidth="22989" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35570" yWindow="1330" windowWidth="22990" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Activity" sheetId="1" r:id="rId1"/>
+    <sheet name="Activity Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Detailed by assay" sheetId="5" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029" fullPrecision="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -65,6 +66,15 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Device Activity by Assay</t>
+  </si>
+  <si>
+    <t>Assay</t>
+  </si>
+  <si>
+    <t>&lt;assayName&gt;</t>
   </si>
 </sst>
 </file>
@@ -584,56 +594,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.35546875" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
     <col min="4" max="4" width="29.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -650,7 +660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -671,4 +681,115 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF3B349-5FA4-4888-8815-0E1E356E16F6}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" customWidth="1"/>
+    <col min="4" max="4" width="36.58203125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.5">
+      <c r="A1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\device_activity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A21402-CFE7-4CC8-9D53-349849BEEB26}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35570" yWindow="1330" windowWidth="22990" windowHeight="16080" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35568" yWindow="1332" windowWidth="22992" windowHeight="16080" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Activity Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Detailed by assay" sheetId="5" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029" fullPrecision="0"/>
+  <calcPr calcId="162913" fullPrecision="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -75,12 +74,18 @@
   </si>
   <si>
     <t>&lt;assayName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
@@ -258,8 +263,36 @@
     <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD7D7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+      <tableStyleElement type="wholeTable" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="0"/>
+    </tableStyle>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -592,58 +625,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="1" max="1" width="31.796875" customWidth="1"/>
+    <col min="2" max="2" width="26.296875" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" customWidth="1"/>
     <col min="4" max="4" width="29.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.796875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -660,7 +693,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -684,19 +717,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF3B349-5FA4-4888-8815-0E1E356E16F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="37.33203125" customWidth="1"/>
-    <col min="4" max="4" width="36.58203125" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="38.796875" customWidth="1"/>
+    <col min="2" max="2" width="38.796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37.296875" customWidth="1"/>
+    <col min="4" max="4" width="36.59765625" customWidth="1"/>
+    <col min="5" max="5" width="19.296875" customWidth="1"/>
+    <col min="6" max="6" width="17.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -706,7 +739,7 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -715,7 +748,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -724,7 +757,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -733,14 +766,14 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -749,7 +782,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
@@ -769,7 +802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>

--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -5,19 +5,30 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-18.04\home\nsabaj\Repositories\aspect\api\templates\device_activity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ahernandez\repos\aspect\api\templates\device_activity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51CD95E7-2D05-4AA0-934A-1EFF3847114B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4FCF52-F79D-4166-BA12-32FC2531CBEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Detailed by assay" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -95,8 +106,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -163,7 +175,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -171,6 +183,8 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,47 +568,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.796875" customWidth="1"/>
-    <col min="2" max="2" width="26.296875" customWidth="1"/>
-    <col min="3" max="3" width="18.19921875" customWidth="1"/>
+    <col min="1" max="1" width="31.75" customWidth="1"/>
+    <col min="2" max="2" width="26.25" customWidth="1"/>
+    <col min="3" max="3" width="18.25" customWidth="1"/>
     <col min="4" max="4" width="29.5" customWidth="1"/>
-    <col min="5" max="5" width="18.796875" customWidth="1"/>
+    <col min="5" max="5" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -611,14 +625,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -636,44 +650,44 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F113"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="38.796875" customWidth="1"/>
-    <col min="3" max="3" width="37.296875" customWidth="1"/>
-    <col min="4" max="4" width="36.59765625" customWidth="1"/>
-    <col min="5" max="5" width="19.296875" customWidth="1"/>
-    <col min="6" max="6" width="17.19921875" customWidth="1"/>
+    <col min="1" max="2" width="38.75" customWidth="1"/>
+    <col min="3" max="3" width="37.25" customWidth="1"/>
+    <col min="4" max="4" width="36.625" customWidth="1"/>
+    <col min="5" max="5" width="19.25" customWidth="1"/>
+    <col min="6" max="6" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -693,7 +707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -703,7 +717,7 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -713,8 +727,323 @@
         <v>14</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D26" s="6"/>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D29" s="6"/>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D30" s="6"/>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="6"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" s="6"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" s="6"/>
+    </row>
+    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D38" s="6"/>
+    </row>
+    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D44" s="6"/>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D47" s="6"/>
+    </row>
+    <row r="48" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D49" s="6"/>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D50" s="6"/>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D51" s="6"/>
+    </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D52" s="6"/>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D53" s="6"/>
+    </row>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D54" s="6"/>
+    </row>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D55" s="6"/>
+    </row>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D56" s="6"/>
+    </row>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D57" s="6"/>
+    </row>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D58" s="6"/>
+    </row>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D59" s="6"/>
+    </row>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D60" s="6"/>
+    </row>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D61" s="6"/>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D62" s="6"/>
+    </row>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D63" s="6"/>
+    </row>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D64" s="6"/>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D65" s="6"/>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D66" s="6"/>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D67" s="6"/>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D68" s="6"/>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D69" s="6"/>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D70" s="6"/>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D71" s="6"/>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D72" s="6"/>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D73" s="6"/>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D74" s="6"/>
+    </row>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D75" s="6"/>
+    </row>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D76" s="6"/>
+    </row>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D77" s="6"/>
+    </row>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D78" s="6"/>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D79" s="6"/>
+    </row>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D80" s="6"/>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D81" s="6"/>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D82" s="6"/>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D83" s="6"/>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D84" s="6"/>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D85" s="6"/>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D86" s="6"/>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D87" s="6"/>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D88" s="6"/>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D89" s="6"/>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D90" s="6"/>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D91" s="6"/>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D92" s="6"/>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D93" s="6"/>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D94" s="6"/>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D95" s="6"/>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D96" s="6"/>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D97" s="6"/>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D98" s="6"/>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D99" s="6"/>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D100" s="6"/>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D101" s="6"/>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D102" s="6"/>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D103" s="6"/>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D104" s="6"/>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D105" s="6"/>
+    </row>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D106" s="6"/>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D107" s="6"/>
+    </row>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D108" s="6"/>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D109" s="6"/>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D110" s="6"/>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D111" s="6"/>
+    </row>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D112" s="6"/>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D113" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C92965-8F27-354B-B243-3CBE7C9B74FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Activity Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Detailed by assay" state="visible" r:id="rId5"/>
+    <sheet name="Activity Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Detailed by assay" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>Device Activity</t>
   </si>
@@ -89,40 +90,40 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-409]mmmm d&quot;, &quot;yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d&quot;, &quot;yyyy;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -139,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -148,26 +149,65 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="slantDashDot">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,144 +521,248 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="11" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G114"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.75" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="26.25" customWidth="1"/>
-    <col min="4" max="4" width="18.25" customWidth="1"/>
-    <col min="5" max="5" width="29.5" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="4" width="26.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="29.5" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2"/>
+    <row r="17" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G113"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="8.625" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.75" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="38.75" customWidth="1"/>
-    <col min="4" max="4" width="37.25" customWidth="1"/>
-    <col min="5" max="5" width="36.625" customWidth="1"/>
-    <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" customWidth="1"/>
+    <col min="4" max="4" width="37.1640625" customWidth="1"/>
+    <col min="5" max="5" width="36.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" customWidth="1"/>
+    <col min="7" max="7" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>21</v>
@@ -636,346 +780,346 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E26" s="6"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E41" s="6"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E42" s="6"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E43" s="6"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E44" s="6"/>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E45" s="6"/>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E46" s="6"/>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E48" s="6"/>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E51" s="6"/>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E54" s="6"/>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E55" s="6"/>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E56" s="6"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E57" s="6"/>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E58" s="6"/>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E59" s="6"/>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E60" s="6"/>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E61" s="6"/>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E62" s="6"/>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E63" s="6"/>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E64" s="6"/>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E65" s="6"/>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E66" s="6"/>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E67" s="6"/>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E68" s="6"/>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E69" s="6"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E70" s="6"/>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E71" s="6"/>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E72" s="6"/>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E73" s="6"/>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E74" s="6"/>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E75" s="6"/>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E76" s="6"/>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E77" s="6"/>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E78" s="6"/>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E79" s="6"/>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E80" s="6"/>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E81" s="6"/>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E82" s="6"/>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E83" s="6"/>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E84" s="6"/>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E85" s="6"/>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E86" s="6"/>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E87" s="6"/>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E88" s="6"/>
-    </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E89" s="6"/>
-    </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E90" s="6"/>
-    </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E91" s="6"/>
-    </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E92" s="6"/>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E93" s="6"/>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E94" s="6"/>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E95" s="6"/>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E96" s="6"/>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E97" s="6"/>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E98" s="6"/>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E99" s="6"/>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E100" s="6"/>
-    </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E101" s="6"/>
-    </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E102" s="6"/>
-    </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E103" s="6"/>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E104" s="6"/>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E105" s="6"/>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E106" s="6"/>
-    </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E107" s="6"/>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E108" s="6"/>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E109" s="6"/>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E110" s="6"/>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E111" s="6"/>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E112" s="6"/>
-    </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E113" s="6"/>
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E29" s="4"/>
+    </row>
+    <row r="30" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E30" s="4"/>
+    </row>
+    <row r="31" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E31" s="4"/>
+    </row>
+    <row r="32" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E36" s="4"/>
+    </row>
+    <row r="37" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E38" s="4"/>
+    </row>
+    <row r="39" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E40" s="4"/>
+    </row>
+    <row r="41" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E42" s="4"/>
+    </row>
+    <row r="43" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E43" s="4"/>
+    </row>
+    <row r="44" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E44" s="4"/>
+    </row>
+    <row r="45" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E45" s="4"/>
+    </row>
+    <row r="46" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E46" s="4"/>
+    </row>
+    <row r="47" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E47" s="4"/>
+    </row>
+    <row r="48" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E48" s="4"/>
+    </row>
+    <row r="49" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E49" s="4"/>
+    </row>
+    <row r="50" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E50" s="4"/>
+    </row>
+    <row r="51" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E51" s="4"/>
+    </row>
+    <row r="52" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E52" s="4"/>
+    </row>
+    <row r="53" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E53" s="4"/>
+    </row>
+    <row r="54" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E54" s="4"/>
+    </row>
+    <row r="55" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E55" s="4"/>
+    </row>
+    <row r="56" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E56" s="4"/>
+    </row>
+    <row r="57" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E57" s="4"/>
+    </row>
+    <row r="58" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E58" s="4"/>
+    </row>
+    <row r="59" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E59" s="4"/>
+    </row>
+    <row r="60" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E60" s="4"/>
+    </row>
+    <row r="61" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E61" s="4"/>
+    </row>
+    <row r="62" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E62" s="4"/>
+    </row>
+    <row r="63" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E64" s="4"/>
+    </row>
+    <row r="65" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E65" s="4"/>
+    </row>
+    <row r="66" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E66" s="4"/>
+    </row>
+    <row r="67" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E67" s="4"/>
+    </row>
+    <row r="68" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E68" s="4"/>
+    </row>
+    <row r="69" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E69" s="4"/>
+    </row>
+    <row r="70" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E70" s="4"/>
+    </row>
+    <row r="71" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E71" s="4"/>
+    </row>
+    <row r="72" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E72" s="4"/>
+    </row>
+    <row r="73" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E73" s="4"/>
+    </row>
+    <row r="74" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E74" s="4"/>
+    </row>
+    <row r="75" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E75" s="4"/>
+    </row>
+    <row r="76" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E77" s="4"/>
+    </row>
+    <row r="78" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E79" s="4"/>
+    </row>
+    <row r="80" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E80" s="4"/>
+    </row>
+    <row r="81" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E81" s="4"/>
+    </row>
+    <row r="82" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E82" s="4"/>
+    </row>
+    <row r="83" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E83" s="4"/>
+    </row>
+    <row r="84" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E85" s="4"/>
+    </row>
+    <row r="86" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E86" s="4"/>
+    </row>
+    <row r="87" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E87" s="4"/>
+    </row>
+    <row r="88" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E88" s="4"/>
+    </row>
+    <row r="89" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E89" s="4"/>
+    </row>
+    <row r="90" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E90" s="4"/>
+    </row>
+    <row r="91" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E91" s="4"/>
+    </row>
+    <row r="92" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E92" s="4"/>
+    </row>
+    <row r="93" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E93" s="4"/>
+    </row>
+    <row r="94" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E94" s="4"/>
+    </row>
+    <row r="95" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E95" s="4"/>
+    </row>
+    <row r="96" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E96" s="4"/>
+    </row>
+    <row r="97" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E97" s="4"/>
+    </row>
+    <row r="98" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E98" s="4"/>
+    </row>
+    <row r="99" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E99" s="4"/>
+    </row>
+    <row r="100" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E100" s="4"/>
+    </row>
+    <row r="101" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E101" s="4"/>
+    </row>
+    <row r="102" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E102" s="4"/>
+    </row>
+    <row r="103" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E103" s="4"/>
+    </row>
+    <row r="104" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E104" s="4"/>
+    </row>
+    <row r="105" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E105" s="4"/>
+    </row>
+    <row r="106" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E106" s="4"/>
+    </row>
+    <row r="107" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E107" s="4"/>
+    </row>
+    <row r="108" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E108" s="4"/>
+    </row>
+    <row r="109" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E109" s="4"/>
+    </row>
+    <row r="110" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E110" s="4"/>
+    </row>
+    <row r="111" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E111" s="4"/>
+    </row>
+    <row r="112" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E112" s="4"/>
+    </row>
+    <row r="113" spans="5:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E113" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -181,16 +181,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -744,7 +743,7 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
     </row>
@@ -754,25 +753,25 @@
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -789,7 +788,7 @@
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -800,319 +799,319 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E9" s="9"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E10" s="9"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="9"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E12" s="9"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E13" s="9"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E14" s="9"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E15" s="9"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E16" s="9"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="9"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="9"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="9"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="9"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="9"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="9"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="9"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="9"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="9"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E26" s="9"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E27" s="9"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E28" s="9"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E29" s="9"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E30" s="9"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="9"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="9"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="9"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="9"/>
+      <c r="E34" s="10"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="9"/>
+      <c r="E35" s="10"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="9"/>
+      <c r="E36" s="10"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="9"/>
+      <c r="E37" s="10"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="9"/>
+      <c r="E38" s="10"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="9"/>
+      <c r="E39" s="10"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="9"/>
+      <c r="E40" s="10"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="9"/>
+      <c r="E41" s="10"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="9"/>
+      <c r="E42" s="10"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E43" s="9"/>
+      <c r="E43" s="10"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="9"/>
+      <c r="E44" s="10"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="9"/>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E46" s="9"/>
+      <c r="E46" s="10"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E47" s="9"/>
+      <c r="E47" s="10"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E48" s="9"/>
+      <c r="E48" s="10"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="9"/>
+      <c r="E49" s="10"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="9"/>
+      <c r="E50" s="10"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="9"/>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="9"/>
+      <c r="E52" s="10"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="9"/>
+      <c r="E53" s="10"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="9"/>
+      <c r="E54" s="10"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="9"/>
+      <c r="E55" s="10"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="9"/>
+      <c r="E56" s="10"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="9"/>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" s="9"/>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E59" s="9"/>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E60" s="9"/>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="9"/>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E62" s="9"/>
+      <c r="E62" s="10"/>
     </row>
     <row r="63" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E63" s="9"/>
+      <c r="E63" s="10"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E64" s="9"/>
+      <c r="E64" s="10"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="9"/>
+      <c r="E65" s="10"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="9"/>
+      <c r="E66" s="10"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="9"/>
+      <c r="E67" s="10"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="9"/>
+      <c r="E68" s="10"/>
     </row>
     <row r="69" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="9"/>
+      <c r="E69" s="10"/>
     </row>
     <row r="70" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="9"/>
+      <c r="E70" s="10"/>
     </row>
     <row r="71" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="9"/>
+      <c r="E71" s="10"/>
     </row>
     <row r="72" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="9"/>
+      <c r="E72" s="10"/>
     </row>
     <row r="73" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="9"/>
+      <c r="E73" s="10"/>
     </row>
     <row r="74" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="9"/>
+      <c r="E74" s="10"/>
     </row>
     <row r="75" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="9"/>
+      <c r="E75" s="10"/>
     </row>
     <row r="76" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="9"/>
+      <c r="E76" s="10"/>
     </row>
     <row r="77" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="9"/>
+      <c r="E77" s="10"/>
     </row>
     <row r="78" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="9"/>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="9"/>
+      <c r="E79" s="10"/>
     </row>
     <row r="80" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="9"/>
+      <c r="E80" s="10"/>
     </row>
     <row r="81" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="9"/>
+      <c r="E81" s="10"/>
     </row>
     <row r="82" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E82" s="9"/>
+      <c r="E82" s="10"/>
     </row>
     <row r="83" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E83" s="9"/>
+      <c r="E83" s="10"/>
     </row>
     <row r="84" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E84" s="9"/>
+      <c r="E84" s="10"/>
     </row>
     <row r="85" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E85" s="9"/>
+      <c r="E85" s="10"/>
     </row>
     <row r="86" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E86" s="9"/>
+      <c r="E86" s="10"/>
     </row>
     <row r="87" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E87" s="9"/>
+      <c r="E87" s="10"/>
     </row>
     <row r="88" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E88" s="9"/>
+      <c r="E88" s="10"/>
     </row>
     <row r="89" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E89" s="9"/>
+      <c r="E89" s="10"/>
     </row>
     <row r="90" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E90" s="9"/>
+      <c r="E90" s="10"/>
     </row>
     <row r="91" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E91" s="9"/>
+      <c r="E91" s="10"/>
     </row>
     <row r="92" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E92" s="9"/>
+      <c r="E92" s="10"/>
     </row>
     <row r="93" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E93" s="9"/>
+      <c r="E93" s="10"/>
     </row>
     <row r="94" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E94" s="9"/>
+      <c r="E94" s="10"/>
     </row>
     <row r="95" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E95" s="9"/>
+      <c r="E95" s="10"/>
     </row>
     <row r="96" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E96" s="9"/>
+      <c r="E96" s="10"/>
     </row>
     <row r="97" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" s="9"/>
+      <c r="E97" s="10"/>
     </row>
     <row r="98" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" s="9"/>
+      <c r="E98" s="10"/>
     </row>
     <row r="99" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" s="9"/>
+      <c r="E99" s="10"/>
     </row>
     <row r="100" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" s="9"/>
+      <c r="E100" s="10"/>
     </row>
     <row r="101" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" s="9"/>
+      <c r="E101" s="10"/>
     </row>
     <row r="102" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" s="9"/>
+      <c r="E102" s="10"/>
     </row>
     <row r="103" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" s="9"/>
+      <c r="E103" s="10"/>
     </row>
     <row r="104" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" s="9"/>
+      <c r="E104" s="10"/>
     </row>
     <row r="105" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" s="9"/>
+      <c r="E105" s="10"/>
     </row>
     <row r="106" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" s="9"/>
+      <c r="E106" s="10"/>
     </row>
     <row r="107" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E107" s="9"/>
+      <c r="E107" s="10"/>
     </row>
     <row r="108" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E108" s="9"/>
+      <c r="E108" s="10"/>
     </row>
     <row r="109" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E109" s="9"/>
+      <c r="E109" s="10"/>
     </row>
     <row r="110" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E110" s="9"/>
+      <c r="E110" s="10"/>
     </row>
     <row r="111" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E111" s="9"/>
+      <c r="E111" s="10"/>
     </row>
     <row r="112" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E112" s="9"/>
+      <c r="E112" s="10"/>
     </row>
     <row r="113" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="9"/>
+      <c r="E113" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/api/templates/device_activity/en.xlsx
+++ b/api/templates/device_activity/en.xlsx
@@ -32,7 +32,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -181,15 +181,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -743,7 +742,7 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -753,25 +752,25 @@
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -788,7 +787,7 @@
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="6" t="s">
@@ -799,319 +798,319 @@
       </c>
     </row>
     <row r="9" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E9" s="10"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E10" s="10"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E11" s="10"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E12" s="10"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E13" s="10"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E15" s="10"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E16" s="10"/>
+      <c r="E16" s="9"/>
     </row>
     <row r="17" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="10"/>
+      <c r="E17" s="9"/>
     </row>
     <row r="18" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18" s="10"/>
+      <c r="E18" s="9"/>
     </row>
     <row r="19" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="10"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="10"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="10"/>
+      <c r="E21" s="9"/>
     </row>
     <row r="22" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22" s="10"/>
+      <c r="E22" s="9"/>
     </row>
     <row r="23" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23" s="10"/>
+      <c r="E23" s="9"/>
     </row>
     <row r="24" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E24" s="10"/>
+      <c r="E24" s="9"/>
     </row>
     <row r="25" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="10"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E26" s="10"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E27" s="10"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E28" s="10"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E29" s="10"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E30" s="10"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E31" s="10"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="10"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" s="10"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="10"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="10"/>
+      <c r="E35" s="9"/>
     </row>
     <row r="36" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" s="10"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" s="10"/>
+      <c r="E37" s="9"/>
     </row>
     <row r="38" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" s="10"/>
+      <c r="E38" s="9"/>
     </row>
     <row r="39" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" s="10"/>
+      <c r="E39" s="9"/>
     </row>
     <row r="40" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="10"/>
+      <c r="E40" s="9"/>
     </row>
     <row r="41" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" s="10"/>
+      <c r="E41" s="9"/>
     </row>
     <row r="42" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" s="10"/>
+      <c r="E42" s="9"/>
     </row>
     <row r="43" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E43" s="10"/>
+      <c r="E43" s="9"/>
     </row>
     <row r="44" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="10"/>
+      <c r="E44" s="9"/>
     </row>
     <row r="45" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E45" s="10"/>
+      <c r="E45" s="9"/>
     </row>
     <row r="46" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E46" s="10"/>
+      <c r="E46" s="9"/>
     </row>
     <row r="47" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E47" s="10"/>
+      <c r="E47" s="9"/>
     </row>
     <row r="48" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E48" s="10"/>
+      <c r="E48" s="9"/>
     </row>
     <row r="49" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E49" s="10"/>
+      <c r="E49" s="9"/>
     </row>
     <row r="50" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="10"/>
+      <c r="E50" s="9"/>
     </row>
     <row r="51" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E51" s="10"/>
+      <c r="E51" s="9"/>
     </row>
     <row r="52" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E52" s="10"/>
+      <c r="E52" s="9"/>
     </row>
     <row r="53" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E53" s="10"/>
+      <c r="E53" s="9"/>
     </row>
     <row r="54" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="10"/>
+      <c r="E54" s="9"/>
     </row>
     <row r="55" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E55" s="10"/>
+      <c r="E55" s="9"/>
     </row>
     <row r="56" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E56" s="10"/>
+      <c r="E56" s="9"/>
     </row>
     <row r="57" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="10"/>
+      <c r="E57" s="9"/>
     </row>
     <row r="58" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E58" s="10"/>
+      <c r="E58" s="9"/>
     </row>
     <row r="59" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E59" s="10"/>
+      <c r="E59" s="9"/>
     </row>
     <row r="60" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E60" s="10"/>
+      <c r="E60" s="9"/>
     </row>
     <row r="61" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E61" s="10"/>
+      <c r="E61" s="9"/>
     </row>
     <row r="62" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E62" s="10"/>
+      <c r="E62" s="9"/>
     </row>
     <row r="63" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E63" s="10"/>
+      <c r="E63" s="9"/>
     </row>
     <row r="64" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E64" s="10"/>
+      <c r="E64" s="9"/>
     </row>
     <row r="65" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E65" s="10"/>
+      <c r="E65" s="9"/>
     </row>
     <row r="66" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E66" s="10"/>
+      <c r="E66" s="9"/>
     </row>
     <row r="67" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E67" s="10"/>
+      <c r="E67" s="9"/>
     </row>
     <row r="68" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E68" s="10"/>
+      <c r="E68" s="9"/>
     </row>
     <row r="69" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E69" s="10"/>
+      <c r="E69" s="9"/>
     </row>
     <row r="70" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E70" s="10"/>
+      <c r="E70" s="9"/>
     </row>
     <row r="71" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E71" s="10"/>
+      <c r="E71" s="9"/>
     </row>
     <row r="72" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E72" s="10"/>
+      <c r="E72" s="9"/>
     </row>
     <row r="73" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E73" s="10"/>
+      <c r="E73" s="9"/>
     </row>
     <row r="74" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E74" s="10"/>
+      <c r="E74" s="9"/>
     </row>
     <row r="75" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E75" s="10"/>
+      <c r="E75" s="9"/>
     </row>
     <row r="76" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E76" s="10"/>
+      <c r="E76" s="9"/>
     </row>
     <row r="77" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E77" s="10"/>
+      <c r="E77" s="9"/>
     </row>
     <row r="78" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E78" s="10"/>
+      <c r="E78" s="9"/>
     </row>
     <row r="79" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E79" s="10"/>
+      <c r="E79" s="9"/>
     </row>
     <row r="80" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E80" s="10"/>
+      <c r="E80" s="9"/>
     </row>
     <row r="81" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E81" s="10"/>
+      <c r="E81" s="9"/>
     </row>
     <row r="82" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E82" s="10"/>
+      <c r="E82" s="9"/>
     </row>
     <row r="83" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E83" s="10"/>
+      <c r="E83" s="9"/>
     </row>
     <row r="84" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E84" s="10"/>
+      <c r="E84" s="9"/>
     </row>
     <row r="85" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E85" s="10"/>
+      <c r="E85" s="9"/>
     </row>
     <row r="86" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E86" s="10"/>
+      <c r="E86" s="9"/>
     </row>
     <row r="87" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E87" s="10"/>
+      <c r="E87" s="9"/>
     </row>
     <row r="88" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E88" s="10"/>
+      <c r="E88" s="9"/>
     </row>
     <row r="89" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E89" s="10"/>
+      <c r="E89" s="9"/>
     </row>
     <row r="90" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E90" s="10"/>
+      <c r="E90" s="9"/>
     </row>
     <row r="91" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E91" s="10"/>
+      <c r="E91" s="9"/>
     </row>
     <row r="92" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E92" s="10"/>
+      <c r="E92" s="9"/>
     </row>
     <row r="93" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E93" s="10"/>
+      <c r="E93" s="9"/>
     </row>
     <row r="94" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E94" s="10"/>
+      <c r="E94" s="9"/>
     </row>
     <row r="95" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E95" s="10"/>
+      <c r="E95" s="9"/>
     </row>
     <row r="96" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E96" s="10"/>
+      <c r="E96" s="9"/>
     </row>
     <row r="97" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E97" s="10"/>
+      <c r="E97" s="9"/>
     </row>
     <row r="98" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E98" s="10"/>
+      <c r="E98" s="9"/>
     </row>
     <row r="99" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E99" s="10"/>
+      <c r="E99" s="9"/>
     </row>
     <row r="100" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E100" s="10"/>
+      <c r="E100" s="9"/>
     </row>
     <row r="101" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E101" s="10"/>
+      <c r="E101" s="9"/>
     </row>
     <row r="102" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E102" s="10"/>
+      <c r="E102" s="9"/>
     </row>
     <row r="103" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E103" s="10"/>
+      <c r="E103" s="9"/>
     </row>
     <row r="104" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E104" s="10"/>
+      <c r="E104" s="9"/>
     </row>
     <row r="105" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E105" s="10"/>
+      <c r="E105" s="9"/>
     </row>
     <row r="106" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E106" s="10"/>
+      <c r="E106" s="9"/>
     </row>
     <row r="107" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E107" s="10"/>
+      <c r="E107" s="9"/>
     </row>
     <row r="108" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E108" s="10"/>
+      <c r="E108" s="9"/>
     </row>
     <row r="109" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E109" s="10"/>
+      <c r="E109" s="9"/>
     </row>
     <row r="110" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E110" s="10"/>
+      <c r="E110" s="9"/>
     </row>
     <row r="111" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E111" s="10"/>
+      <c r="E111" s="9"/>
     </row>
     <row r="112" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E112" s="10"/>
+      <c r="E112" s="9"/>
     </row>
     <row r="113" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E113" s="10"/>
+      <c r="E113" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
